--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:00 | 차트: 95개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:56 | 차트: 95개</t>
         </is>
       </c>
     </row>
@@ -577,22 +577,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>8건</t>
+          <t>4.00건</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>15건</t>
+          <t>7.50건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>+7건</t>
+          <t>+3.5건</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -614,22 +614,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>8건</t>
+          <t>4.00건</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>13건</t>
+          <t>6.50건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>+5건</t>
+          <t>+2.5건</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>9명</t>
+          <t>4.50명</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>13명</t>
+          <t>6.50명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>+4명</t>
+          <t>+2.0명</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1058,22 +1058,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원</t>
+          <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>4명</t>
+          <t>2.00명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>5명</t>
+          <t>2.50명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>+1명</t>
+          <t>+0.5명</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1126,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>▲ 실시간 호출 건수 (+87.5%)</t>
+          <t>▲ 실시간 호출 건수(일평균) (+87.5%)</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>▲ 이동완료 호출 건수 (+62.5%)</t>
+          <t>▲ 이동완료 호출 건수(일평균) (+62.5%)</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>미탑승 건수</t>
+          <t>미탑승 건수(일평균)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1436,12 +1436,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>호출취소 건수</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>배차실패 건수</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>▲ 총 탑승객 수 (+44.4%)</t>
+          <t>▲ 총 탑승객 수(일평균) (+44.4%)</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1665,7 +1665,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대(12~14시) 가호출 성공률</t>
+          <t>가호출 성공률(평일)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>+8.3%p</t>
+          <t>-10.5%p</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>+16.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 가호출 성공률 변화</t>
+          <t>평일 가호출 성공률 변화</t>
         </is>
       </c>
     </row>
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공/실패 회원</t>
+          <t>가호출 성공률(주말)</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>+4.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>+160.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>가호출 실패 경험 이용자 증가</t>
+          <t>주말 가호출 성공률 변화</t>
         </is>
       </c>
     </row>
@@ -2135,32 +2135,32 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>피크 시간대(12~14시) 가호출 성공률</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+8.3%p</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+16.7%</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 매칭 실패</t>
+          <t>피크 시간대 가호출 성공률 변화</t>
         </is>
       </c>
     </row>
@@ -2172,150 +2172,150 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>가호출 수</t>
+          <t>가호출 성공/실패 회원(일평균)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>+4.00</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>+160.0%</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>가호출 실패 경험 이용자 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>차량 공급 부족에 따른 매칭 실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>가호출 수(일평균)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>+7.00</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>+175.0%</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>수요 급증 대비 공급 부족</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>▼ 평균 대당 운행거리 (-18.9%)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>평균 대당 운행거리</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>일간 평균 대당 운행거리</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>-18.9%</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>일별 운행거리 편차</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>평균 대당 운행거리</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>실시간 호출 건수</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>+3.50</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>+87.5%</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>수요 변동에 따른 운행거리 변화</t>
         </is>
       </c>
     </row>
@@ -2327,150 +2327,150 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>일간 평균 대당 운행거리</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>-18.9%</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>일별 운행거리 편차</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>평균 대당 운행거리</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>+3.50</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>+87.5%</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>수요 변동에 따른 운행거리 변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>평균 대당 운행거리</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>운행차량 대수</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>+0.00</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>차량 수 변동에 따른 대당 거리 변화</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>▲ DAU (일간 활성 회원) (+120.0%)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>DAU (일간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>WAU (주간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>주간 활성도 추이 연동</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>DAU (일간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>+0.50</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>신규 유입 증감 영향</t>
         </is>
       </c>
     </row>
@@ -2482,32 +2482,32 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>활성 회원 평균연령</t>
+          <t>WAU (주간 활성 회원)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>+4.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>이용자 평균 연령 변화</t>
+          <t>주간 활성도 추이 연동</t>
         </is>
       </c>
     </row>
@@ -2519,32 +2519,32 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+0.50</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>+25.0%</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>서비스 품질 불만에 따른 이탈</t>
+          <t>신규 유입 증감 영향</t>
         </is>
       </c>
     </row>
@@ -2556,148 +2556,222 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>활성 회원 평균연령</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>+4.00</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>이용자 평균 연령 변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>서비스 품질 불만에 따른 이탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>평균 대기시간</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>4.31</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>3.65</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>-0.66</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>-15.3%</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>대기시간 증가에 따른 이탈</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>▲ 신규 지역 회원 (+25.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>▲ 신규 지역 회원(일평균) (+25.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>누적 지역 회원</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>누적 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>9.00</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>+5.00</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>+55.6%</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>전체 회원 기반 성장세</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>가호출 순 회원</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>가호출 순 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>5.50</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>+3.00</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>+120.0%</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>가입 후 미이용(잠재 이탈) 회원</t>
         </is>
@@ -2708,13 +2782,13 @@
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2726,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2797,32 +2871,32 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>상위 10% 대기시간</t>
+          <t>평균 대기시간(평일)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>극단적 장시간 대기 사례 발생</t>
+          <t>평일 대기시간 변화</t>
         </is>
       </c>
     </row>
@@ -2834,22 +2908,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>장시간 대기(30분+) 비율</t>
+          <t>평균 대기시간(주말)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>+0.0%p</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2859,7 +2933,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>30분 이상 장시간 대기 비중</t>
+          <t>주말 대기시간 변화</t>
         </is>
       </c>
     </row>
@@ -2871,32 +2945,32 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>상위 10% 대기시간</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 대기 증가</t>
+          <t>극단적 장시간 대기 사례 발생</t>
         </is>
       </c>
     </row>
@@ -2908,150 +2982,150 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>장시간 대기(30분+) 비율</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%p</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>30분 이상 장시간 대기 비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>차량 공급 부족에 따른 대기 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>7.50</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>+3.50</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>+87.5%</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>수요 대비 공급 불균형</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>─ 운행차량 대수 (+0.0%)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>일별 운행 차량 수</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>+0.00</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>특정일 차량 미운행</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>근무 이행률</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>+0.00</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>기사 근무 미이행</t>
         </is>
       </c>
     </row>
@@ -3063,150 +3137,150 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>배차실패 건수</t>
+          <t>일별 운행 차량 수</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>특정일 차량 미운행</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>근무 이행률</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>기사 근무 미이행</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>배차실패 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>+1.00</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>+inf%</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>차량 감소에 따른 배차 실패 연쇄</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>▼ 평균 대당 운행시간 (-0.3%)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>평균 대당 운행시간</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>차량별 운행 시간</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>+0.00</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>특정 차량 운행 시간 편차</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>평균 대당 운행시간</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>평균 근무시간</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>+0.00</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>공차 대기 시간 증가</t>
         </is>
       </c>
     </row>
@@ -3218,30 +3292,104 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>차량별 운행 시간</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>특정 차량 운행 시간 편차</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>평균 대당 운행시간</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>평균 근무시간</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>공차 대기 시간 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>평균 대당 운행시간</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>차량 대당 탑승객</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>수요 감소에 따른 공회전</t>
         </is>
@@ -3250,9 +3398,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3264,7 +3412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -3280,40 +3428,26 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>• 수요 증가: 호출(+88%), 이동완료(+62%), 탑승객(+44%) 모두 상승 — 분석기간 운행 2일(03/16,03/17), 비교기간 2일</t>
+          <t>• 대기시간 개선: 4.31분 → 3.65분 (-15%) — 특히 03/17 상위10% 대기시간 9.5분으로 극단치 발생</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>• 이동완료율 100.0% → 86.7% (-13.3%p): 호출 15건 중 13건 완료 (호출취소 0건, 배차실패 2건)</t>
+          <t>• 가호출 성공률 급락: 90.0% → 79.5%, 가호출 시도 일평균 11.0건</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>• 대기시간 개선: 4.31분 → 3.65분 (-15%) — 특히 03/17 상위10% 대기시간 9.5분으로 극단치 발생</t>
+          <t>• 성장 지표 긍정적: DAU +120%, 누적 15명</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>• 가호출 성공률 급락: 90.0% → 79.5%, 가호출 시도 일평균 11.0건</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>• 성장 지표 긍정적: DAU +120%, 신규회원 4→5명(+25%), 누적 15명 — 이용자 기반 확대 추세</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>• 이동시간 증가: 3.92분 → 4.50분 (+15%) — 우회비율은 소폭 증가, 경로 효율성 저하</t>
         </is>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:15 | 차트: 95개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:29 | 차트: 95개</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>호출 증가의 실질 완료 전환 정도</t>
+          <t>동반 증가 (62%)</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>수요 급증에 따른 품질 저하 우려</t>
+          <t>감소 전환 (15%)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>전화 호출 채널 비중 변화</t>
+          <t>비중 역방향 감소 (56%)</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>앱 호출 채널 비중 변화</t>
+          <t>비중 큰 폭 증가, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>현장(직접) 호출 비중 변화</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>배차 후 미탑승(노쇼) 발생</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>이용자 자발적 취소</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>배차 매칭 실패</t>
+          <t>신규 발생</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>동승 비율 변화에 따른 탑승객 증감</t>
+          <t>동반 증가 (44%)</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>고령 이용자 호출 비중 변화</t>
+          <t>소폭 역방향 감소</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>성인 이용자 호출 비중 변화</t>
+          <t>신규 발생</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>어린이/청소년 호출 비중 변화</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>극단적 우회 경로 발생</t>
+          <t>90% 증가, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>우회 경로 증가가 이동시간 상승 유발</t>
+          <t>소폭 증가, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>동승 증가로 경유지 추가</t>
+          <t>동반 증가 (44%)</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간 변화</t>
+          <t>소폭 증가, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간 변화</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>경로 우회에 따른 이동시간 증가</t>
+          <t>56% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>평일 가호출 성공률 변화</t>
+          <t>비중 감소 (12%)</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>주말 가호출 성공률 변화</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 가호출 성공률 변화</t>
+          <t>소폭 역방향 증가</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>가호출 실패 경험 이용자 증가</t>
+          <t>역방향 증가 (160%)</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 매칭 실패</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>수요 급증 대비 공급 부족</t>
+          <t>역방향 증가 (175%)</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>일별 운행거리 편차</t>
+          <t>동반 감소 (19%)</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>수요 변동에 따른 운행거리 변화</t>
+          <t>역방향 증가 (88%)</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>차량 수 변동에 따른 대당 거리 변화</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>주간 활성도 추이 연동</t>
+          <t>분석기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>신규 유입 증감 영향</t>
+          <t>소폭 증가, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>이용자 평균 연령 변화</t>
+          <t>소폭 증가, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>서비스 품질 불만에 따른 이탈</t>
+          <t>감소 전환 (12%)</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>대기시간 증가에 따른 이탈</t>
+          <t>감소 전환 (15%)</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>전체 회원 기반 성장세</t>
+          <t>56% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>가입 후 미이용(잠재 이탈) 회원</t>
+          <t>120% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 대기시간 변화</t>
+          <t>동반 감소 (15%)</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 대기시간 변화</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>극단적 장시간 대기 사례 발생</t>
+          <t>소폭 감소, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>30분 이상 장시간 대기 비중</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 대기 증가</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>수요 대비 공급 불균형</t>
+          <t>역방향 증가 (88%)</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>특정일 차량 미운행</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>기사 근무 미이행</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>차량 감소에 따른 배차 실패 연쇄</t>
+          <t>신규 발생</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>특정 차량 운행 시간 편차</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>공차 대기 시간 증가</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>수요 감소에 따른 공회전</t>
+          <t>분석기간 데이터 없음</t>
         </is>
       </c>
     </row>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:29 | 차트: 95개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:30 | 차트: 95개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 09:54 | 차트: 95개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 10:12 | 차트: 109개</t>
         </is>
       </c>
     </row>
@@ -698,22 +698,22 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.5명</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.0명</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>+44.4%</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -994,22 +994,22 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15.5%p</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>-37.3%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>감소</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1702,7 +1702,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>▲ 평균 우회비율 (+55.6%)</t>
+          <t>▲ 대당 탑승객 수 (+44.4%)</t>
         </is>
       </c>
     </row>
@@ -1746,81 +1746,81 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>대당 탑승객 수</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>상위 10% 우회비율</t>
+          <t>대당 탑승객 수(평일)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>+90.3%</t>
+          <t>+44.4%</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>2.0배, 우회 심화</t>
+          <t>평일 6.5명 (44% 증가)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>대당 탑승객 수</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>평균 이동시간</t>
+          <t>대당 탑승객 수(주말)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>+14.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>3.9→4.5분 증가</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>대당 탑승객 수</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1854,815 +1854,815 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>+87.5%</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>88% 증가, 주요 요인</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>▲ 평균 이동시간 (+14.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>1대 유지, 증차 여지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>▲ 평균 우회비율 (+55.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>평균 이동시간</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>피크 시간대(12~14시) 이동시간</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>+3.2%</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>3.2분 안정</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>평균 이동시간</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>비피크 시간대(9~11시) 이동시간</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>상위 10% 우회비율</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>+90.3%</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>2.0배, 우회 심화</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>평균 이동시간</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>+14.7%</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>3.9→4.5분 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>평균 우회비율</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>+55.6%</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>0.8→1.3배 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>▼ 가호출 성공률 (-11.6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>동승 인원 분포(일평균)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>+44.4%</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>동반 증가 (44%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>▲ 평균 이동시간 (+14.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률(평일)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>79.5%</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>-10.5%p</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>-11.6%</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>평일 80% (12% 감소)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률(주말)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>평균 이동시간</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대(12~14시) 가호출 성공률</t>
+          <t>피크 시간대(12~14시) 이동시간</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>+8.3%p</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>+16.7%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>피크 58% (17% 증가)</t>
+          <t>3.2분 안정</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>평균 이동시간</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공/실패 회원(일평균)</t>
+          <t>비피크 시간대(9~11시) 이동시간</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>+160.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2.5→6.5명 증가</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>+55.6%</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>0.8→1.3배 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>▼ 가호출 성공률 (-11.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>가호출 성공률</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>+0.0</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>1대 유지, 증차 여지 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>가호출 수(일평균)</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>+175.0%</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>가호출 증가, 실호출 미전환</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>▼ 평균 대당 운행거리 (-18.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률(평일)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>79.5%</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>-10.5%p</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>평일 80% (12% 감소)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>평균 대당 운행거리</t>
+          <t>가호출 성공률</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>일간 평균 대당 운행거리</t>
+          <t>가호출 성공률(주말)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>동반 감소 (19%)</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>평균 대당 운행거리</t>
+          <t>가호출 성공률</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수(일평균)</t>
+          <t>피크 시간대(12~14시) 가호출 성공률</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>+8.3%p</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>+87.5%</t>
+          <t>+16.7%</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>역방향 증가 (88%)</t>
+          <t>피크 58% (17% 증가)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>평균 대당 운행거리</t>
+          <t>가호출 성공률</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>가호출 성공/실패 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>+160.0%</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>2.5→6.5명 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>운행차량 대수</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>+0.0</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>▲ DAU (일간 활성 회원) (+120.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>가호출 수(일평균)</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>+175.0%</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>가호출 증가, 실호출 미전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>▼ 평균 대당 운행거리 (-18.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>DAU (일간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>WAU (주간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>분석기간 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>DAU (일간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원(일평균)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>신규 2.5명/일 (25% 증가)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>평균 대당 운행거리</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>활성 회원 평균연령</t>
+          <t>일간 평균 대당 운행거리</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>평균 69세 (6% 증가)</t>
+          <t>동반 감소 (19%)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>평균 대당 운행거리</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>-10.5%p</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>+87.5%</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>소폭 역방향 감소</t>
+          <t>역방향 증가 (88%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>평균 대당 운행거리</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>평균 대기시간</t>
+          <t>운행차량 대수</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>4.3→3.6분 감소</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>▲ 신규 지역 회원(일평균) (+25.0%)</t>
+          <t>▲ DAU (일간 활성 회원) (+120.0%)</t>
         </is>
       </c>
     </row>
@@ -2706,89 +2706,319 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원(일평균)</t>
+          <t>DAU (일간 활성 회원)</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>누적 지역 회원(일평균)</t>
+          <t>WAU (주간 활성 회원)</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>+55.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>누적 14명 (56% 증가)</t>
+          <t>분석기간 데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>신규 2.5명/일 (25% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>활성 회원 평균연령</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>평균 69세 (6% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>79.5%</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-10.5%p</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>소폭 역방향 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>-15.3%</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>4.3→3.6분 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>▲ 신규 지역 회원(일평균) (+25.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>누적 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>+55.6%</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>누적 14명 (56% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>가호출 순 회원(일평균)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>+3.0</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>+120.0%</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>2.5→5.5명 증가</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A36:G36"/>
+  <mergeCells count="11">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2869,7 +3099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3445,31 +3675,150 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+44.4%</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>역방향 증가 (44%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>▼ 평균 경로이탈비중 (-37.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>+55.6%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>0.8→1.3배 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>+14.7%</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>3.9→4.5분 증가</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:40 | 차트: 109개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:43 | 차트: 109개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:47 | 차트: 109개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:52 | 차트: 109개</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>개선</t>
+          <t>감소</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>⚠ 저하</t>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>저하</t>
+          <t>증가</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
@@ -935,7 +935,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>저하</t>
+          <t>감소</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>⚠ 개선</t>
+          <t>⚠ 감소</t>
         </is>
       </c>
     </row>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:52 | 차트: 109개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:53 | 차트: 109개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
+++ b/shucle_report/해안면/20260316_20260317/report_해안면_20260316_20260317.xlsx
@@ -896,7 +896,7 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
